--- a/Team-Data/2011-12/4-8-2011-12.xlsx
+++ b/Team-Data/2011-12/4-8-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>2.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -757,7 +824,7 @@
         <v>16</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK2" t="n">
         <v>14</v>
@@ -766,7 +833,7 @@
         <v>9</v>
       </c>
       <c r="AM2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN2" t="n">
         <v>5</v>
@@ -778,7 +845,7 @@
         <v>23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR2" t="n">
         <v>27</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -843,37 +910,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F3" t="n">
         <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>0.571</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="J3" t="n">
-        <v>76.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.459</v>
+        <v>0.456</v>
       </c>
       <c r="L3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M3" t="n">
         <v>14.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.366</v>
+        <v>0.364</v>
       </c>
       <c r="O3" t="n">
         <v>15.5</v>
@@ -882,19 +949,19 @@
         <v>19.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R3" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="S3" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T3" t="n">
         <v>38.6</v>
       </c>
       <c r="U3" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V3" t="n">
         <v>14.9</v>
@@ -909,22 +976,22 @@
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA3" t="n">
         <v>18.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>91.5</v>
+        <v>91.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE3" t="n">
         <v>11</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>10</v>
       </c>
       <c r="AF3" t="n">
         <v>11</v>
@@ -933,7 +1000,7 @@
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI3" t="n">
         <v>23</v>
@@ -942,7 +1009,7 @@
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL3" t="n">
         <v>22</v>
@@ -951,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="AN3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ3" t="n">
         <v>5</v>
@@ -966,37 +1033,37 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT3" t="n">
         <v>30</v>
       </c>
       <c r="AU3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
         <v>24</v>
       </c>
       <c r="BB3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-12.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1121,7 +1188,7 @@
         <v>30</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK4" t="n">
         <v>30</v>
@@ -1139,10 +1206,10 @@
         <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR4" t="n">
         <v>25</v>
@@ -1154,7 +1221,7 @@
         <v>28</v>
       </c>
       <c r="AU4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV4" t="n">
         <v>13</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -1207,64 +1274,64 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" t="n">
         <v>43</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>0.754</v>
+        <v>0.768</v>
       </c>
       <c r="H5" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I5" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="J5" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L5" t="n">
         <v>6.3</v>
       </c>
       <c r="M5" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="O5" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="P5" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0.725</v>
       </c>
       <c r="R5" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="S5" t="n">
-        <v>32.3</v>
+        <v>32.1</v>
       </c>
       <c r="T5" t="n">
-        <v>46.3</v>
+        <v>46</v>
       </c>
       <c r="U5" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="V5" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="W5" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X5" t="n">
         <v>5.9</v>
@@ -1273,19 +1340,19 @@
         <v>5.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="AB5" t="n">
         <v>96.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1300,13 +1367,13 @@
         <v>26</v>
       </c>
       <c r="AI5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL5" t="n">
         <v>17</v>
@@ -1321,7 +1388,7 @@
         <v>22</v>
       </c>
       <c r="AP5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
         <v>27</v>
@@ -1339,7 +1406,7 @@
         <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AW5" t="n">
         <v>23</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -1389,37 +1456,37 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" t="n">
         <v>18</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="H6" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I6" t="n">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="J6" t="n">
-        <v>81.5</v>
+        <v>81.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.422</v>
+        <v>0.421</v>
       </c>
       <c r="L6" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M6" t="n">
         <v>19.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.351</v>
+        <v>0.347</v>
       </c>
       <c r="O6" t="n">
         <v>18</v>
@@ -1428,19 +1495,19 @@
         <v>25.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.709</v>
+        <v>0.708</v>
       </c>
       <c r="R6" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S6" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T6" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U6" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="V6" t="n">
         <v>15.3</v>
@@ -1452,22 +1519,22 @@
         <v>4.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.59999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>-6.3</v>
+        <v>-6.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE6" t="n">
         <v>27</v>
@@ -1479,25 +1546,25 @@
         <v>26</v>
       </c>
       <c r="AH6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AI6" t="n">
         <v>27</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AK6" t="n">
         <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN6" t="n">
         <v>14</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>13</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
@@ -1515,10 +1582,10 @@
         <v>24</v>
       </c>
       <c r="AT6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV6" t="n">
         <v>23</v>
@@ -1539,7 +1606,7 @@
         <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF7" t="n">
         <v>13</v>
@@ -1661,7 +1728,7 @@
         <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI7" t="n">
         <v>19</v>
@@ -1694,7 +1761,7 @@
         <v>28</v>
       </c>
       <c r="AS7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
         <v>14</v>
@@ -1703,7 +1770,7 @@
         <v>15</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
         <v>4</v>
@@ -1718,13 +1785,13 @@
         <v>7</v>
       </c>
       <c r="BA7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB7" t="n">
         <v>20</v>
       </c>
       <c r="BC7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -1831,10 +1898,10 @@
         <v>1.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF8" t="n">
         <v>13</v>
@@ -1843,13 +1910,13 @@
         <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK8" t="n">
         <v>4</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR8" t="n">
         <v>17</v>
@@ -1891,7 +1958,7 @@
         <v>10</v>
       </c>
       <c r="AX8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY8" t="n">
         <v>30</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -1935,46 +2002,46 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E9" t="n">
         <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>0.375</v>
+        <v>0.382</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="J9" t="n">
-        <v>78.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="K9" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L9" t="n">
         <v>4.5</v>
       </c>
       <c r="M9" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="N9" t="n">
-        <v>0.341</v>
+        <v>0.346</v>
       </c>
       <c r="O9" t="n">
         <v>16.6</v>
       </c>
       <c r="P9" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.75</v>
+        <v>0.751</v>
       </c>
       <c r="R9" t="n">
         <v>11.9</v>
@@ -1986,10 +2053,10 @@
         <v>40</v>
       </c>
       <c r="U9" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="V9" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="W9" t="n">
         <v>7</v>
@@ -2001,19 +2068,19 @@
         <v>5.4</v>
       </c>
       <c r="Z9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA9" t="n">
         <v>19.7</v>
       </c>
-      <c r="AA9" t="n">
-        <v>19.8</v>
-      </c>
       <c r="AB9" t="n">
-        <v>90.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5.4</v>
+        <v>-5.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AE9" t="n">
         <v>23</v>
@@ -2025,7 +2092,7 @@
         <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI9" t="n">
         <v>26</v>
@@ -2034,7 +2101,7 @@
         <v>25</v>
       </c>
       <c r="AK9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL9" t="n">
         <v>26</v>
@@ -2043,19 +2110,19 @@
         <v>27</v>
       </c>
       <c r="AN9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
         <v>15</v>
       </c>
       <c r="AP9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
         <v>30</v>
@@ -2064,22 +2131,22 @@
         <v>27</v>
       </c>
       <c r="AU9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV9" t="n">
         <v>28</v>
       </c>
       <c r="AW9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY9" t="n">
         <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA9" t="n">
         <v>15</v>
@@ -2088,7 +2155,7 @@
         <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2</v>
       </c>
       <c r="AD10" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
@@ -2207,7 +2274,7 @@
         <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
         <v>6</v>
@@ -2216,7 +2283,7 @@
         <v>12</v>
       </c>
       <c r="AK10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL10" t="n">
         <v>3</v>
@@ -2234,7 +2301,7 @@
         <v>29</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR10" t="n">
         <v>29</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
         <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>0.554</v>
+        <v>0.545</v>
       </c>
       <c r="H11" t="n">
         <v>48.7</v>
       </c>
       <c r="I11" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J11" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K11" t="n">
         <v>0.454</v>
@@ -2326,34 +2393,34 @@
         <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.363</v>
+        <v>0.362</v>
       </c>
       <c r="O11" t="n">
         <v>15.6</v>
       </c>
       <c r="P11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="R11" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S11" t="n">
         <v>30.5</v>
       </c>
       <c r="T11" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U11" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V11" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W11" t="n">
         <v>7.4</v>
@@ -2368,19 +2435,19 @@
         <v>20.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AE11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF11" t="n">
         <v>12</v>
@@ -2395,10 +2462,10 @@
         <v>5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL11" t="n">
         <v>12</v>
@@ -2407,13 +2474,13 @@
         <v>17</v>
       </c>
       <c r="AN11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ11" t="n">
         <v>3</v>
@@ -2425,34 +2492,34 @@
         <v>18</v>
       </c>
       <c r="AT11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV11" t="n">
         <v>15</v>
       </c>
       <c r="AW11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY11" t="n">
         <v>20</v>
       </c>
       <c r="AZ11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>2.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
@@ -2571,7 +2638,7 @@
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI12" t="n">
         <v>22</v>
@@ -2589,7 +2656,7 @@
         <v>22</v>
       </c>
       <c r="AN12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2601,13 +2668,13 @@
         <v>6</v>
       </c>
       <c r="AR12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS12" t="n">
         <v>12</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
         <v>30</v>
@@ -2619,7 +2686,7 @@
         <v>14</v>
       </c>
       <c r="AX12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY12" t="n">
         <v>27</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
         <v>6</v>
@@ -2759,7 +2826,7 @@
         <v>13</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK13" t="n">
         <v>12</v>
@@ -2783,7 +2850,7 @@
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
         <v>23</v>
@@ -2792,7 +2859,7 @@
         <v>18</v>
       </c>
       <c r="AU13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV13" t="n">
         <v>3</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>1.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2944,7 +3011,7 @@
         <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL14" t="n">
         <v>23</v>
@@ -2965,7 +3032,7 @@
         <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2986,7 +3053,7 @@
         <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ14" t="n">
         <v>3</v>
@@ -2998,7 +3065,7 @@
         <v>15</v>
       </c>
       <c r="BC14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>1.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
         <v>10</v>
@@ -3117,7 +3184,7 @@
         <v>10</v>
       </c>
       <c r="AH15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI15" t="n">
         <v>14</v>
@@ -3150,7 +3217,7 @@
         <v>7</v>
       </c>
       <c r="AS15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT15" t="n">
         <v>15</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -3209,37 +3276,37 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F16" t="n">
         <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.727</v>
+        <v>0.722</v>
       </c>
       <c r="H16" t="n">
         <v>48.6</v>
       </c>
       <c r="I16" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J16" t="n">
-        <v>79.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.474</v>
+        <v>0.475</v>
       </c>
       <c r="L16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O16" t="n">
         <v>19.5</v>
@@ -3248,25 +3315,25 @@
         <v>25.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.774</v>
+        <v>0.777</v>
       </c>
       <c r="R16" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S16" t="n">
         <v>31.4</v>
       </c>
       <c r="T16" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U16" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V16" t="n">
         <v>15</v>
       </c>
       <c r="W16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X16" t="n">
         <v>5.5</v>
@@ -3275,19 +3342,19 @@
         <v>4.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>100.2</v>
+        <v>100.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3326,7 +3393,7 @@
         <v>7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR16" t="n">
         <v>26</v>
@@ -3338,7 +3405,7 @@
         <v>20</v>
       </c>
       <c r="AU16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV16" t="n">
         <v>18</v>
@@ -3347,10 +3414,10 @@
         <v>3</v>
       </c>
       <c r="AX16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ16" t="n">
         <v>17</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -3469,19 +3536,19 @@
         <v>0.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF17" t="n">
         <v>19</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>19</v>
       </c>
       <c r="AH17" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
         <v>4</v>
@@ -3490,16 +3557,16 @@
         <v>2</v>
       </c>
       <c r="AK17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM17" t="n">
         <v>16</v>
       </c>
       <c r="AN17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO17" t="n">
         <v>17</v>
@@ -3517,13 +3584,13 @@
         <v>26</v>
       </c>
       <c r="AT17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW17" t="n">
         <v>5</v>
@@ -3541,10 +3608,10 @@
         <v>19</v>
       </c>
       <c r="BB17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
         <v>21</v>
@@ -3663,13 +3730,13 @@
         <v>21</v>
       </c>
       <c r="AH18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI18" t="n">
         <v>20</v>
       </c>
       <c r="AJ18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK18" t="n">
         <v>26</v>
@@ -3690,7 +3757,7 @@
         <v>6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
         <v>6</v>
@@ -3705,7 +3772,7 @@
         <v>25</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -3755,28 +3822,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F19" t="n">
         <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>0.362</v>
+        <v>0.351</v>
       </c>
       <c r="H19" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>34.3</v>
+        <v>34.1</v>
       </c>
       <c r="J19" t="n">
-        <v>80.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.427</v>
+        <v>0.426</v>
       </c>
       <c r="L19" t="n">
         <v>8</v>
@@ -3785,25 +3852,25 @@
         <v>23.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O19" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P19" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.773</v>
+        <v>0.772</v>
       </c>
       <c r="R19" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S19" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="T19" t="n">
-        <v>40.5</v>
+        <v>40.3</v>
       </c>
       <c r="U19" t="n">
         <v>20.1</v>
@@ -3812,7 +3879,7 @@
         <v>15.2</v>
       </c>
       <c r="W19" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X19" t="n">
         <v>4.1</v>
@@ -3821,34 +3888,34 @@
         <v>4.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.7</v>
+        <v>93.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.1</v>
+        <v>-5.3</v>
       </c>
       <c r="AD19" t="n">
         <v>1</v>
       </c>
       <c r="AE19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG19" t="n">
         <v>25</v>
       </c>
-      <c r="AG19" t="n">
-        <v>24</v>
-      </c>
       <c r="AH19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AI19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ19" t="n">
         <v>22</v>
@@ -3863,7 +3930,7 @@
         <v>2</v>
       </c>
       <c r="AN19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO19" t="n">
         <v>13</v>
@@ -3872,10 +3939,10 @@
         <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS19" t="n">
         <v>29</v>
@@ -3884,19 +3951,19 @@
         <v>26</v>
       </c>
       <c r="AU19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV19" t="n">
         <v>21</v>
       </c>
       <c r="AW19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY19" t="n">
         <v>16</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>29</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>14</v>
       </c>
       <c r="AZ19" t="n">
         <v>10</v>
@@ -3905,10 +3972,10 @@
         <v>16</v>
       </c>
       <c r="BB19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4027,7 +4094,7 @@
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4045,7 +4112,7 @@
         <v>30</v>
       </c>
       <c r="AN20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO20" t="n">
         <v>27</v>
@@ -4072,7 +4139,7 @@
         <v>26</v>
       </c>
       <c r="AW20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX20" t="n">
         <v>20</v>
@@ -4081,10 +4148,10 @@
         <v>25</v>
       </c>
       <c r="AZ20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB20" t="n">
         <v>29</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -4119,49 +4186,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F21" t="n">
         <v>27</v>
       </c>
       <c r="G21" t="n">
-        <v>0.518</v>
+        <v>0.509</v>
       </c>
       <c r="H21" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J21" t="n">
-        <v>81.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K21" t="n">
-        <v>0.437</v>
+        <v>0.439</v>
       </c>
       <c r="L21" t="n">
         <v>7.3</v>
       </c>
       <c r="M21" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0.319</v>
+        <v>0.321</v>
       </c>
       <c r="O21" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P21" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q21" t="n">
         <v>0.741</v>
       </c>
       <c r="R21" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S21" t="n">
         <v>30.8</v>
@@ -4173,7 +4240,7 @@
         <v>19.7</v>
       </c>
       <c r="V21" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="W21" t="n">
         <v>9.5</v>
@@ -4182,7 +4249,7 @@
         <v>4.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z21" t="n">
         <v>21.3</v>
@@ -4194,31 +4261,31 @@
         <v>97.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AF21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AH21" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
       </c>
       <c r="AJ21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
         <v>8</v>
@@ -4242,7 +4309,7 @@
         <v>14</v>
       </c>
       <c r="AS21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT21" t="n">
         <v>12</v>
@@ -4251,7 +4318,7 @@
         <v>23</v>
       </c>
       <c r="AV21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW21" t="n">
         <v>2</v>
@@ -4269,7 +4336,7 @@
         <v>2</v>
       </c>
       <c r="BB21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC21" t="n">
         <v>6</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E22" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F22" t="n">
         <v>15</v>
       </c>
       <c r="G22" t="n">
-        <v>0.732</v>
+        <v>0.727</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="J22" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="K22" t="n">
-        <v>0.475</v>
+        <v>0.476</v>
       </c>
       <c r="L22" t="n">
         <v>7.1</v>
@@ -4331,7 +4398,7 @@
         <v>19.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O22" t="n">
         <v>20.9</v>
@@ -4346,7 +4413,7 @@
         <v>10.7</v>
       </c>
       <c r="S22" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T22" t="n">
         <v>43.3</v>
@@ -4364,22 +4431,22 @@
         <v>8</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA22" t="n">
         <v>20</v>
       </c>
       <c r="AB22" t="n">
-        <v>102.7</v>
+        <v>102.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,10 +4458,10 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ22" t="n">
         <v>26</v>
@@ -4406,7 +4473,7 @@
         <v>11</v>
       </c>
       <c r="AM22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN22" t="n">
         <v>11</v>
@@ -4427,25 +4494,25 @@
         <v>2</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA22" t="n">
         <v>14</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>1.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>9</v>
@@ -4573,10 +4640,10 @@
         <v>9</v>
       </c>
       <c r="AH23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ23" t="n">
         <v>29</v>
@@ -4597,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="AP23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4609,7 +4676,7 @@
         <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AU23" t="n">
         <v>22</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -4665,64 +4732,64 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E24" t="n">
         <v>29</v>
       </c>
       <c r="F24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G24" t="n">
-        <v>0.518</v>
+        <v>0.527</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J24" t="n">
-        <v>83.5</v>
+        <v>83.7</v>
       </c>
       <c r="K24" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L24" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="M24" t="n">
         <v>14.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0.364</v>
+        <v>0.366</v>
       </c>
       <c r="O24" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="P24" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.739</v>
+        <v>0.738</v>
       </c>
       <c r="R24" t="n">
         <v>10.5</v>
       </c>
       <c r="S24" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T24" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U24" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V24" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="W24" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X24" t="n">
         <v>5</v>
@@ -4737,19 +4804,19 @@
         <v>16.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
       </c>
       <c r="AF24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG24" t="n">
         <v>15</v>
@@ -4758,10 +4825,10 @@
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK24" t="n">
         <v>15</v>
@@ -4773,7 +4840,7 @@
         <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4788,13 +4855,13 @@
         <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT24" t="n">
         <v>9</v>
       </c>
       <c r="AU24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV24" t="n">
         <v>1</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -4925,28 +4992,28 @@
         <v>-0.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
       </c>
       <c r="AF25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH25" t="n">
         <v>30</v>
       </c>
       <c r="AI25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ25" t="n">
         <v>11</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL25" t="n">
         <v>15</v>
@@ -4955,13 +5022,13 @@
         <v>13</v>
       </c>
       <c r="AN25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO25" t="n">
         <v>18</v>
       </c>
       <c r="AP25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ25" t="n">
         <v>15</v>
@@ -4979,7 +5046,7 @@
         <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW25" t="n">
         <v>27</v>
@@ -5000,7 +5067,7 @@
         <v>11</v>
       </c>
       <c r="BC25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>0.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>20</v>
@@ -5119,7 +5186,7 @@
         <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI26" t="n">
         <v>17</v>
@@ -5179,7 +5246,7 @@
         <v>13</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC26" t="n">
         <v>18</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -5211,25 +5278,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E27" t="n">
         <v>19</v>
       </c>
       <c r="F27" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G27" t="n">
-        <v>0.333</v>
+        <v>0.339</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
       </c>
       <c r="I27" t="n">
-        <v>37.1</v>
+        <v>37.3</v>
       </c>
       <c r="J27" t="n">
-        <v>86.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K27" t="n">
         <v>0.431</v>
@@ -5238,19 +5305,19 @@
         <v>6.2</v>
       </c>
       <c r="M27" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N27" t="n">
-        <v>0.312</v>
+        <v>0.31</v>
       </c>
       <c r="O27" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P27" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.741</v>
+        <v>0.746</v>
       </c>
       <c r="R27" t="n">
         <v>13.7</v>
@@ -5259,13 +5326,13 @@
         <v>29.8</v>
       </c>
       <c r="T27" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U27" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="V27" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W27" t="n">
         <v>8.4</v>
@@ -5274,34 +5341,34 @@
         <v>4.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA27" t="n">
         <v>20.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5.8</v>
+        <v>-5.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
       </c>
       <c r="AF27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG27" t="n">
         <v>27</v>
       </c>
-      <c r="AG27" t="n">
-        <v>26</v>
-      </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI27" t="n">
         <v>12</v>
@@ -5316,7 +5383,7 @@
         <v>18</v>
       </c>
       <c r="AM27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN27" t="n">
         <v>28</v>
@@ -5325,7 +5392,7 @@
         <v>10</v>
       </c>
       <c r="AP27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ27" t="n">
         <v>20</v>
@@ -5334,7 +5401,7 @@
         <v>2</v>
       </c>
       <c r="AS27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT27" t="n">
         <v>5</v>
@@ -5343,7 +5410,7 @@
         <v>26</v>
       </c>
       <c r="AV27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW27" t="n">
         <v>6</v>
@@ -5355,13 +5422,13 @@
         <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA27" t="n">
         <v>9</v>
       </c>
       <c r="BB27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC27" t="n">
         <v>27</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E28" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F28" t="n">
         <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>0.741</v>
+        <v>0.736</v>
       </c>
       <c r="H28" t="n">
         <v>48.4</v>
       </c>
       <c r="I28" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J28" t="n">
-        <v>82.7</v>
+        <v>83</v>
       </c>
       <c r="K28" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L28" t="n">
         <v>8.199999999999999</v>
@@ -5423,61 +5490,61 @@
         <v>21.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.387</v>
+        <v>0.389</v>
       </c>
       <c r="O28" t="n">
-        <v>15.9</v>
+        <v>15.5</v>
       </c>
       <c r="P28" t="n">
-        <v>21.6</v>
+        <v>21.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.736</v>
+        <v>0.731</v>
       </c>
       <c r="R28" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S28" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T28" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U28" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V28" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="W28" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X28" t="n">
         <v>4.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.3</v>
+        <v>102.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
       </c>
       <c r="AF28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG28" t="n">
         <v>2</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK28" t="n">
         <v>3</v>
@@ -5504,13 +5571,13 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR28" t="n">
         <v>24</v>
@@ -5528,7 +5595,7 @@
         <v>2</v>
       </c>
       <c r="AW28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX28" t="n">
         <v>24</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E29" t="n">
         <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G29" t="n">
-        <v>0.351</v>
+        <v>0.357</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="J29" t="n">
         <v>78.3</v>
       </c>
       <c r="K29" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L29" t="n">
         <v>5.5</v>
@@ -5608,13 +5675,13 @@
         <v>0.335</v>
       </c>
       <c r="O29" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P29" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R29" t="n">
         <v>10.5</v>
@@ -5623,49 +5690,49 @@
         <v>31</v>
       </c>
       <c r="T29" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U29" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="V29" t="n">
         <v>15.1</v>
       </c>
       <c r="W29" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X29" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>91.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.4</v>
+        <v>-3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF29" t="n">
         <v>25</v>
       </c>
       <c r="AG29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI29" t="n">
         <v>25</v>
@@ -5674,7 +5741,7 @@
         <v>27</v>
       </c>
       <c r="AK29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL29" t="n">
         <v>21</v>
@@ -5683,7 +5750,7 @@
         <v>20</v>
       </c>
       <c r="AN29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO29" t="n">
         <v>14</v>
@@ -5713,10 +5780,10 @@
         <v>26</v>
       </c>
       <c r="AX29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5725,7 +5792,7 @@
         <v>23</v>
       </c>
       <c r="BB29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC29" t="n">
         <v>23</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -5757,37 +5824,37 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
       </c>
       <c r="F30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G30" t="n">
-        <v>0.509</v>
+        <v>0.518</v>
       </c>
       <c r="H30" t="n">
         <v>48.8</v>
       </c>
       <c r="I30" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J30" t="n">
-        <v>84.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L30" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="M30" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.31</v>
+        <v>0.308</v>
       </c>
       <c r="O30" t="n">
         <v>18.8</v>
@@ -5796,7 +5863,7 @@
         <v>25</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.75</v>
+        <v>0.752</v>
       </c>
       <c r="R30" t="n">
         <v>13.1</v>
@@ -5811,7 +5878,7 @@
         <v>21.8</v>
       </c>
       <c r="V30" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W30" t="n">
         <v>8.300000000000001</v>
@@ -5820,31 +5887,31 @@
         <v>5.7</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA30" t="n">
         <v>20.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>99.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
         <v>15</v>
       </c>
       <c r="AF30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH30" t="n">
         <v>2</v>
@@ -5856,7 +5923,7 @@
         <v>3</v>
       </c>
       <c r="AK30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL30" t="n">
         <v>30</v>
@@ -5874,7 +5941,7 @@
         <v>8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AR30" t="n">
         <v>3</v>
@@ -5886,7 +5953,7 @@
         <v>4</v>
       </c>
       <c r="AU30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV30" t="n">
         <v>11</v>
@@ -5898,7 +5965,7 @@
         <v>4</v>
       </c>
       <c r="AY30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ30" t="n">
         <v>29</v>
@@ -5907,10 +5974,10 @@
         <v>8</v>
       </c>
       <c r="BB30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-7</v>
       </c>
       <c r="AD31" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6029,16 +6096,16 @@
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI31" t="n">
         <v>18</v>
       </c>
       <c r="AJ31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6050,10 +6117,10 @@
         <v>25</v>
       </c>
       <c r="AO31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ31" t="n">
         <v>26</v>
@@ -6068,7 +6135,7 @@
         <v>22</v>
       </c>
       <c r="AU31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV31" t="n">
         <v>25</v>
@@ -6089,7 +6156,7 @@
         <v>22</v>
       </c>
       <c r="BB31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC31" t="n">
         <v>29</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-8-2011-12</t>
+          <t>2012-04-08</t>
         </is>
       </c>
     </row>
